--- a/data/lists_fishing_styles.xlsx
+++ b/data/lists_fishing_styles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\storage.slu.se\home_2$\eoar0001\Documents\ARMELLONI_SLU\RiskAnalysis\LEK\interviews_round2_aug2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A25AB8D-5FA8-46FF-9638-CA589A7FE9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B968CD-CE4B-4DA8-8689-BF33646C9D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fishing_style" sheetId="1" r:id="rId1"/>
@@ -106,9 +106,6 @@
     <t>inland</t>
   </si>
   <si>
-    <t>costal</t>
-  </si>
-  <si>
     <t>offshore</t>
   </si>
   <si>
@@ -155,6 +152,9 @@
   </si>
   <si>
     <t>all</t>
+  </si>
+  <si>
+    <t>trap</t>
   </si>
 </sst>
 </file>
@@ -508,7 +508,7 @@
         <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -522,13 +522,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -542,13 +542,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -562,13 +562,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -588,7 +588,7 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -608,7 +608,7 @@
         <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -628,7 +628,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -642,13 +642,13 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -662,13 +662,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -682,13 +682,13 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -696,7 +696,7 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -708,7 +708,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -728,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -768,7 +768,7 @@
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -788,7 +788,7 @@
         <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -808,7 +808,7 @@
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -828,7 +828,7 @@
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -848,7 +848,7 @@
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -862,13 +862,13 @@
         <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -888,7 +888,7 @@
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -902,13 +902,13 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -922,13 +922,13 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -942,13 +942,13 @@
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -962,13 +962,13 @@
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s">
         <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -982,13 +982,13 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
         <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1002,13 +1002,13 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1022,13 +1022,13 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1042,13 +1042,13 @@
         <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" t="s">
         <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1068,7 +1068,7 @@
         <v>25</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1088,7 +1088,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1105,10 +1105,10 @@
         <v>22</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1125,10 +1125,10 @@
         <v>22</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1148,7 +1148,7 @@
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1168,7 +1168,7 @@
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1188,7 +1188,7 @@
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1202,13 +1202,13 @@
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1228,7 +1228,7 @@
         <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1248,7 +1248,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1274,28 +1274,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1306,7 +1306,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1338,7 +1338,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1370,7 +1370,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1402,7 +1402,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1434,7 +1434,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1466,7 +1466,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1498,7 +1498,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8">
         <v>1</v>

--- a/data/lists_fishing_styles.xlsx
+++ b/data/lists_fishing_styles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B968CD-CE4B-4DA8-8689-BF33646C9D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B723A1C-9C7D-4C52-9A00-4945ED7E1C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/lists_fishing_styles.xlsx
+++ b/data/lists_fishing_styles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B723A1C-9C7D-4C52-9A00-4945ED7E1C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050D92CC-F7A3-4BBC-94E1-5A38A3DF44B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29630" yWindow="-5930" windowWidth="19870" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fishing_style" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="43">
   <si>
     <t>id</t>
   </si>
@@ -67,12 +67,6 @@
     <t>herring</t>
   </si>
   <si>
-    <t>fixed trap</t>
-  </si>
-  <si>
-    <t>gillnets</t>
-  </si>
-  <si>
     <t>whitefish</t>
   </si>
   <si>
@@ -94,9 +88,6 @@
     <t>sprat</t>
   </si>
   <si>
-    <t>trawl</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
@@ -154,7 +145,16 @@
     <t>all</t>
   </si>
   <si>
-    <t>trap</t>
+    <t>gns_spf</t>
+  </si>
+  <si>
+    <t>gns_fws</t>
+  </si>
+  <si>
+    <t>fpn_ana</t>
+  </si>
+  <si>
+    <t>otm</t>
   </si>
 </sst>
 </file>
@@ -482,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.88671875" customWidth="1"/>
@@ -505,10 +505,10 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -522,13 +522,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -542,13 +542,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -562,13 +562,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -582,13 +582,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -602,13 +602,13 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -622,13 +622,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -642,13 +642,13 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -659,16 +659,16 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -679,41 +679,41 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -722,33 +722,33 @@
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="A13" s="2">
         <v>3</v>
       </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
-        <v>6</v>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>38</v>
+        <v>41</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -759,50 +759,50 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>3</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -816,19 +816,19 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -836,59 +836,59 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" t="s">
-        <v>10</v>
-      </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -896,19 +896,19 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -916,19 +916,19 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -936,19 +936,19 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -956,19 +956,19 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -976,19 +976,19 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -996,139 +996,139 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
         <v>5</v>
       </c>
-      <c r="D26" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>5</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>5</v>
-      </c>
-      <c r="B27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>5</v>
-      </c>
-      <c r="B28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>5</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>5</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
         <v>6</v>
       </c>
-      <c r="B32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" t="s">
-        <v>21</v>
-      </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1139,16 +1139,16 @@
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1159,96 +1159,36 @@
         <v>9</v>
       </c>
       <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>7</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D34" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>7</v>
-      </c>
-      <c r="B35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>7</v>
-      </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>7</v>
-      </c>
-      <c r="B37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
-        <v>7</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>39</v>
+      <c r="D35" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1274,28 +1214,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1306,7 +1246,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1338,7 +1278,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1370,7 +1310,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1399,10 +1339,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1431,10 +1371,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1463,10 +1403,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1498,7 +1438,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D8">
         <v>1</v>
